--- a/Collections/EURO/Greece/#EURO#Greece#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Greece/#EURO#Greece#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Greece\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B5F383-F4F1-4969-9E8F-69492960C660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3168E6-ADB5-44F4-8761-BA589E1581B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -652,7 +655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="170">
   <si>
     <t>-</t>
   </si>
@@ -1139,6 +1142,30 @@
   </si>
   <si>
     <t>Subtype_3#Special_distinctions_1</t>
+  </si>
+  <si>
+    <t>19.005.000</t>
+  </si>
+  <si>
+    <t>5.000</t>
+  </si>
+  <si>
+    <t>20.005.000</t>
+  </si>
+  <si>
+    <t>7.005.000</t>
+  </si>
+  <si>
+    <t>22.005.000</t>
+  </si>
+  <si>
+    <t>13.005.000</t>
+  </si>
+  <si>
+    <t>17.005.000</t>
+  </si>
+  <si>
+    <t>14.505.000</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1561,351 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="112">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2103,9 +2474,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="44" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2374,7 +2745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3075,6 +3446,62 @@
         <v/>
       </c>
     </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <f t="shared" ref="I26:I27" si="3">IF(OR(AND(G26&gt;1,G26&lt;&gt;"-"),AND(H26&gt;1,H26&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
@@ -3085,11 +3512,26 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="68" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G21 G23 G25">
+    <cfRule type="containsText" dxfId="110" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3101,10 +3543,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G21 G23 G25">
-    <cfRule type="containsText" dxfId="67" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="109" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3116,13 +3560,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="66" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="108" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3133,12 +3577,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="65" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="107" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H27">
+    <cfRule type="containsText" dxfId="106" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3150,27 +3609,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="64" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
+  <conditionalFormatting sqref="G22 G24 G26">
+    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3182,10 +3624,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G22">
-    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3205,7 +3649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3846,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="str">
-        <f t="shared" ref="I23:I25" si="1">IF(OR(AND(G23&gt;1,G23&lt;&gt;"-"),AND(H23&gt;1,H23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I23:I27" si="1">IF(OR(AND(G23&gt;1,G23&lt;&gt;"-"),AND(H23&gt;1,H23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3902,6 +4346,62 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3916,11 +4416,60 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G5:G21 G23 G25">
-    <cfRule type="containsText" dxfId="61" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G21 G23 G25">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="103" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="containsText" dxfId="102" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="101" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3932,12 +4481,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="60" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="100" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3949,12 +4498,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="59" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="99" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3966,10 +4515,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="58" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H22:H25">
+    <cfRule type="containsText" dxfId="98" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H25">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3981,12 +4532,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="G22 G24">
+    <cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3998,12 +4547,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="56" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26:H27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4015,12 +4564,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="55" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4032,10 +4579,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G22">
-    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4055,7 +4604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4752,7 +5301,63 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="str">
-        <f t="shared" ref="I25" si="2">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-"),AND(H25&gt;1,H25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I25:I27" si="2">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-"),AND(H25&gt;1,H25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4766,11 +5371,62 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G16:G21 G5:G14 G23 G25">
-    <cfRule type="containsText" dxfId="53" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:G21 G5:G14 G23 G25">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="95" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="containsText" dxfId="94" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="93" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4782,12 +5438,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="52" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4799,12 +5453,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="51" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="91" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4816,12 +5470,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="50" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="90" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4833,10 +5487,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="49" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H22:H25">
+    <cfRule type="containsText" dxfId="89" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H25">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4848,12 +5504,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="48" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="G22 G24">
+    <cfRule type="containsText" dxfId="88" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4865,12 +5519,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="47" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26:H27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4882,12 +5536,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="46" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4899,10 +5551,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G22">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4922,7 +5576,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5630,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" ref="J23:J25" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J23:J27" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5692,6 +6346,68 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5706,11 +6422,124 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="containsText" dxfId="86" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21 H23 H25">
+    <cfRule type="containsText" dxfId="85" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="84" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="83" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="82" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="containsText" dxfId="81" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="80" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5722,12 +6551,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="43" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
+  <conditionalFormatting sqref="H24">
+    <cfRule type="containsText" dxfId="79" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5739,76 +6568,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21 H23 H25">
-    <cfRule type="containsText" dxfId="42" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5820,9 +6585,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -5835,12 +6600,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5860,7 +6625,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6568,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" ref="J23:J25" si="1">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J23:J27" si="1">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6630,6 +7395,68 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6644,11 +7471,109 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="35" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H21 H23 H25">
+    <cfRule type="containsText" dxfId="76" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="75" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="74" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="containsText" dxfId="73" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22 H24">
+    <cfRule type="containsText" dxfId="72" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6660,61 +7585,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H21 H23 H25">
-    <cfRule type="containsText" dxfId="33" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6726,12 +7602,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6743,10 +7617,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24 H22">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7474,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" ref="J23:J25" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J23:J27" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="U23" s="23"/>
@@ -7541,7 +8417,67 @@
         <v/>
       </c>
     </row>
+    <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="U27" s="23"/>
     </row>
   </sheetData>
@@ -7554,11 +8490,124 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="containsText" dxfId="70" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="containsText" dxfId="69" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="68" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="67" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="66" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H23 H25">
+    <cfRule type="containsText" dxfId="64" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7570,12 +8619,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
+  <conditionalFormatting sqref="H24">
+    <cfRule type="containsText" dxfId="63" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7587,76 +8634,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7668,9 +8651,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H23 H25">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -7683,10 +8666,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7706,7 +8691,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -8414,7 +9399,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" ref="J23:J25" si="3">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J23:J27" si="3">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8476,6 +9461,68 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -8490,11 +9537,109 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="containsText" dxfId="61" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="containsText" dxfId="60" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="59" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="58" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="57" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="containsText" dxfId="56" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8506,12 +9651,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="18" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
+  <conditionalFormatting sqref="H22:H24">
+    <cfRule type="containsText" dxfId="55" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8523,9 +9666,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="54" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -8538,61 +9681,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8604,9 +9698,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H24">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -8619,10 +9713,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9350,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" ref="J23:J25" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J23:J27" si="2">IF(OR(AND(H23&gt;1,H23&lt;&gt;"-"),AND(I23&gt;1,I23&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -9416,7 +10512,67 @@
         <v/>
       </c>
     </row>
+    <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="U27" s="23"/>
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9432,11 +10588,124 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="containsText" dxfId="52" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I21">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H21">
+    <cfRule type="containsText" dxfId="51" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="50" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="48" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="containsText" dxfId="47" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I25">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H25">
+    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9448,76 +10717,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I21">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
+  <conditionalFormatting sqref="I26:I27">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:I27">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9529,12 +10734,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9546,10 +10749,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/EURO/Greece/#EURO#Greece#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Greece/#EURO#Greece#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Greece\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3168E6-ADB5-44F4-8761-BA589E1581B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4736A702-55F7-419A-BA9E-A5B71C426C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -1561,14 +1561,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="112">
+  <dxfs count="91">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1745,175 +1746,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2474,9 +2306,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="44" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3512,7 +3344,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="111" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3529,7 +3361,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G21 G23 G25">
-    <cfRule type="containsText" dxfId="110" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -3544,7 +3376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="109" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3561,7 +3393,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="108" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3578,7 +3410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="107" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -3593,7 +3425,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H27">
-    <cfRule type="containsText" dxfId="106" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3609,8 +3441,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24 G26">
-    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G24 G22 G26">
+    <cfRule type="containsText" dxfId="84" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3625,7 +3457,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4416,7 +4248,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G5:G21 G23 G25">
-    <cfRule type="containsText" dxfId="104" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4433,7 +4265,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="103" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4450,7 +4282,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="102" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4467,7 +4299,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="101" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -4482,7 +4314,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="100" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4499,7 +4331,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="99" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4516,7 +4348,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="98" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4532,8 +4364,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
-    <cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G24 G22">
+    <cfRule type="containsText" dxfId="75" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -4548,7 +4380,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4565,7 +4397,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4580,7 +4412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5371,7 +5203,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G16:G21 G5:G14 G23 G25">
-    <cfRule type="containsText" dxfId="96" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5388,7 +5220,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="95" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5405,7 +5237,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="94" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5422,7 +5254,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="93" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5439,7 +5271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -5454,7 +5286,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="91" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5471,7 +5303,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="90" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5488,7 +5320,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="89" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5504,8 +5336,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
-    <cfRule type="containsText" dxfId="88" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G24 G22">
+    <cfRule type="containsText" dxfId="63" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -5520,7 +5352,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5537,7 +5369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5552,7 +5384,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6422,7 +6254,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="87" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6439,7 +6271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="86" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6456,7 +6288,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21 H23 H25">
-    <cfRule type="containsText" dxfId="85" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -6471,7 +6303,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="84" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -6486,7 +6318,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="83" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6503,7 +6335,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="82" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6520,7 +6352,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="81" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6537,7 +6369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22">
-    <cfRule type="containsText" dxfId="80" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -6552,7 +6384,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="79" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6569,7 +6401,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6586,7 +6418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -6601,7 +6433,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7471,7 +7303,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="78" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7488,7 +7320,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7505,7 +7337,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H21 H23 H25">
-    <cfRule type="containsText" dxfId="76" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -7520,12 +7352,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="75" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="74" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7554,7 +7386,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="73" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7570,8 +7402,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H24">
-    <cfRule type="containsText" dxfId="72" priority="13" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H24 H22">
+    <cfRule type="containsText" dxfId="41" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -7586,7 +7418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7603,7 +7435,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -7618,7 +7450,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8490,7 +8322,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="71" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8507,7 +8339,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="70" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8524,7 +8356,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="69" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -8539,7 +8371,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="68" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -8554,7 +8386,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="67" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8571,7 +8403,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="66" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8588,7 +8420,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8605,7 +8437,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H23 H25">
-    <cfRule type="containsText" dxfId="64" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -8620,7 +8452,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="63" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -8635,7 +8467,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8652,7 +8484,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -8667,7 +8499,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8959,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>0</v>
@@ -9537,7 +9369,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="62" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9554,7 +9386,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="61" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9571,7 +9403,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="60" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -9586,7 +9418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="59" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -9601,7 +9433,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="58" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9618,7 +9450,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="57" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9635,7 +9467,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="56" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9652,7 +9484,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H24">
-    <cfRule type="containsText" dxfId="55" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -9667,7 +9499,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="54" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -9682,7 +9514,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9699,7 +9531,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -9714,7 +9546,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10588,7 +10420,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="53" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10605,7 +10437,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I21">
-    <cfRule type="containsText" dxfId="52" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10622,7 +10454,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H21">
-    <cfRule type="containsText" dxfId="51" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -10637,7 +10469,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="50" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -10652,7 +10484,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10669,7 +10501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="48" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10686,7 +10518,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I25">
-    <cfRule type="containsText" dxfId="47" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10703,7 +10535,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -10718,7 +10550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10735,7 +10567,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -10750,7 +10582,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
